--- a/outputs/Riverside House - Fenster Pricing Document (house format).xlsx
+++ b/outputs/Riverside House - Fenster Pricing Document (house format).xlsx
@@ -78,7 +78,7 @@
     <numFmt numFmtId="166" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="General_)"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -193,6 +193,9 @@
       <name val="Aptos"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -662,7 +665,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -926,6 +929,15 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -2379,7 +2391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:V35"/>
+  <dimension ref="B2:V45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="4.6640625" customWidth="1" min="1" max="1"/>
@@ -3496,7 +3508,7 @@
     <row r="31">
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>** This pricing document should be read in conjunction with the Terms and Conditions.</t>
+          <t>** This pricing document should be read with Fenster Glazing &amp; Locks Ltd's Standard Terms and Conditions (issue 31.05.2026), a copy of which accompanies this document.</t>
         </is>
       </c>
       <c r="D31" s="20" t="n"/>
@@ -3507,40 +3519,129 @@
       <c r="D32" s="20" t="n"/>
       <c r="E32" s="20" t="n"/>
     </row>
-    <row r="33">
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="20" t="n"/>
-      <c r="E33" s="20" t="n"/>
-    </row>
-    <row r="34">
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="20" t="n"/>
-    </row>
-    <row r="35">
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="20" t="n"/>
-      <c r="E35" s="20" t="n"/>
+    <row r="33" ht="15" customHeight="1">
+      <c r="C33" s="114" t="inlineStr">
+        <is>
+          <t>EXCLUSIONS - the following are NOT included in the price above</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="C34" s="115" t="inlineStr">
+        <is>
+          <t>- Design responsibility - design calculations, structural calculations and engineer approvals, including any wind loading check and the structural design of fixings, unless specifically included within our scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="C35" s="115" t="inlineStr">
+        <is>
+          <t>- Structural alterations - forming, enlarging or making good any structural opening, to be completed by the main contractor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="C36" s="116" t="inlineStr">
+        <is>
+          <t>- AOV control system - smoke control panel, mains and battery-backed supply, cabling, containment, fire-brigade override at ground floor access level, and commissioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="C37" s="116" t="inlineStr">
+        <is>
+          <t>- Testing - on or off site testing of the completed smoke ventilation system</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="C38" s="116" t="inlineStr">
+        <is>
+          <t>- Anti-fall protection to Part K, where the vent cill sits below 1100mm from finished floor level, and any preventative measures for trap hazard below 2.5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="C39" s="116" t="inlineStr">
+        <is>
+          <t>- Access and lifting equipment - scaffold, MEWPs, towers, forklift and the like</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="C40" s="116" t="inlineStr">
+        <is>
+          <t>- Site storage - materials will be delivered to site</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="C41" s="116" t="inlineStr">
+        <is>
+          <t>- Site welfare - welfare facilities, power, water, lighting</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="C42" s="116" t="inlineStr">
+        <is>
+          <t>- Waste removal, internal finishing, fire stopping and final clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="C43" s="116" t="inlineStr">
+        <is>
+          <t>- Traffic management - road closures, street licences, parking suspensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="C44" s="116" t="inlineStr">
+        <is>
+          <t>- Dimensions provided by others are assumed to be accurate. Any additional costs arising from incorrect dimensions will be treated as a variation and charged accordingly</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="C45" s="116" t="inlineStr">
+        <is>
+          <t>- The free area stated is GEOMETRIC. No aerodynamic figure has been provided by the manufacturer and none is warranted by this quotation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="30">
+    <mergeCell ref="C36:I36"/>
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="C37:I37"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C7:D7"/>
     <mergeCell ref="F28:H28"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="C42:I42"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="C45:I45"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C41:I41"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C44:I44"/>
+    <mergeCell ref="C40:I40"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C43:I43"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>

--- a/outputs/Riverside House - Fenster Pricing Document (house format).xlsx
+++ b/outputs/Riverside House - Fenster Pricing Document (house format).xlsx
@@ -8,64 +8,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Document " sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="Access_Control">'[1]Item Budgets'!$B$156:$B$167</definedName>
-    <definedName name="Audio_Visual">'[1]Item Budgets'!$B$167:$B$178</definedName>
-    <definedName name="Beam">#REF!</definedName>
-    <definedName name="Beams">#REF!</definedName>
-    <definedName name="BeamTon">#REF!</definedName>
-    <definedName name="Channel">#REF!</definedName>
-    <definedName name="Channels">#REF!</definedName>
-    <definedName name="ChannelTon">#REF!</definedName>
-    <definedName name="CHSs">#REF!</definedName>
-    <definedName name="Column">#REF!</definedName>
-    <definedName name="Columns">#REF!</definedName>
-    <definedName name="ColumnTon">#REF!</definedName>
-    <definedName name="CONTAINMENT">'[1]Item Budgets'!$B$95:$B$111</definedName>
-    <definedName name="DISTRIBUTION">'[1]Item Budgets'!$B$123:$B$134</definedName>
-    <definedName name="EMERGENCY_LIGHTING">'[1]Item Budgets'!$B$23:$B$34</definedName>
-    <definedName name="Equal">#REF!</definedName>
-    <definedName name="EqualTon">#REF!</definedName>
-    <definedName name="FIRE_ALARM">'[1]Item Budgets'!$B$112:$B$123</definedName>
-    <definedName name="Heating_Interface">'[1]Item Budgets'!$B$178:$B$189</definedName>
-    <definedName name="Lighting">'[1]Item Budgets'!$B$4:$B$23</definedName>
-    <definedName name="LIGHTING_CONTROL">'[1]Item Budgets'!$B$34:$B$45</definedName>
-    <definedName name="LIST">[1]Containment!#REF!</definedName>
-    <definedName name="List1">#REF!</definedName>
-    <definedName name="List2">#REF!</definedName>
-    <definedName name="List3">#REF!</definedName>
-    <definedName name="Mechanical_Supplies">'[1]Item Budgets'!$B$134:$B$145</definedName>
-    <definedName name="MISCELLANEOUS">'[1]Item Budgets'!$B$189:$B$207</definedName>
-    <definedName name="PCFTon">#REF!</definedName>
-    <definedName name="PFC">#REF!</definedName>
-    <definedName name="PFCs">#REF!</definedName>
-    <definedName name="PFCTon">#REF!</definedName>
-    <definedName name="PRELIMS">'[1]Item Budgets'!$B$207:$B$216</definedName>
-    <definedName name="RHS">#REF!</definedName>
-    <definedName name="RHSs">#REF!</definedName>
-    <definedName name="RHSTon">#REF!</definedName>
-    <definedName name="RSJ">#REF!</definedName>
-    <definedName name="RSJs">#REF!</definedName>
-    <definedName name="RSJTon">#REF!</definedName>
-    <definedName name="SHS">#REF!</definedName>
-    <definedName name="SHSs">#REF!</definedName>
-    <definedName name="SHSsTon">#REF!</definedName>
-    <definedName name="SHSTon">#REF!</definedName>
-    <definedName name="Site_Temporaries">'[1]Item Budgets'!$B$217:$B$228</definedName>
-    <definedName name="SMALL_POWER">'[1]Item Budgets'!$B$45:$B$95</definedName>
-    <definedName name="Steels">#REF!</definedName>
-    <definedName name="Type">#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!</definedName>
-    <definedName name="Types">'[2]Type List'!$A$2:$A$8</definedName>
-    <definedName name="Unequal">#REF!</definedName>
-    <definedName name="UnequalTon">#REF!</definedName>
-    <definedName name="Ventilation">'[1]Item Budgets'!$B$145:$B$156</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Pricing Document '!$2:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Pricing Document '!$C$1:$I$31</definedName>
-  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -1001,1093 +943,6 @@
     <clientData/>
   </twoCellAnchor>
 </wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Checklist"/>
-      <sheetName val="Summary"/>
-      <sheetName val="Price Breakdown"/>
-      <sheetName val="Item Budgets"/>
-      <sheetName val="Containment"/>
-      <sheetName val="Project Type"/>
-      <sheetName val="Procore Measure"/>
-      <sheetName val="Item Categories"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>LIGHTING</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>Ceiling Mounted Luminaire</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>Double Sided Illuminated Emergency Exit Sign</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>Floor Mounted Luminaire - X12</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>Illuminated Emergency Exit Sign</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>Illuminated Emergency Exit Sign With Direction Arrow</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>Led Emergency Downlight</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>Led Strip Light</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>Lighting Wiring Point</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>Linear Luminaire</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>Photocell</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>PV Inverted, Relay &amp; DC/AC Isolator + Single Socket Outlet And RJ45 For Data For PV Panels</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>Recessed Modular Downlighter</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v xml:space="preserve">Recessed Modular Uplighter </v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>Wall Mounted Luminaire</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>Wall Mounted Luminaire - Emergency</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>EMERGENCY LIGHTING</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>EL Item 1</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>EL Item 2</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>EL Item 3</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>EL Item 4</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>EL Item 5</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>EL Item 6</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>EL Item 7</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>EL Item 8</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>LIGHTING CONTROL</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>LC Item 1</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>LC Item 2</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="str">
-            <v>LC Item 3</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="str">
-            <v>LC Item 4</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39" t="str">
-            <v>LC Item 5</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40" t="str">
-            <v>LC Item 6</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41" t="str">
-            <v>LC Item 7</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42" t="str">
-            <v>LC Item 8</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45" t="str">
-            <v>SMALL POWER</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46" t="str">
-            <v>1 Gang Switch</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47" t="str">
-            <v>1 Gang Dimmer Switch</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48" t="str">
-            <v>2 Gang Switch</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49" t="str">
-            <v>20A Oven Control Unit</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50" t="str">
-            <v>40A Cooker Control Unit</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51" t="str">
-            <v>Automatic Transfer Switch</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="B52" t="str">
-            <v>Booster Switch</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="B53" t="str">
-            <v>Cooker Connection Point</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="B54" t="str">
-            <v>Data Outlet</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="B55" t="str">
-            <v>Door Bell</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="B56" t="str">
-            <v>Doorbell Push</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="B57" t="str">
-            <v>Double Pole Switch</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="B58" t="str">
-            <v>Heat Alarm</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="B59" t="str">
-            <v>Heat Detector</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="B60" t="str">
-            <v>Intermediate Switch</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="B61" t="str">
-            <v>Ip65 Switch With Neon</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="B62" t="str">
-            <v>Junction Box</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="B63" t="str">
-            <v>Multi Sensor Smoke/Heat Detector</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="B64" t="str">
-            <v>Override Switches For External Lighting</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="B65" t="str">
-            <v>Power Supply To The X11 Led Lights</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="B66" t="str">
-            <v>Patch Panel</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="B67" t="str">
-            <v>Presence Detector</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="B68" t="str">
-            <v>Shaver Socket</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="B69" t="str">
-            <v>Single Switch Socket Outlet</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="B70" t="str">
-            <v>Smoke Alarm</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="B71" t="str">
-            <v>Smoke Detector</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="B72" t="str">
-            <v>Smoke/Heat/Co Alarm Remote Control Switch</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="B73" t="str">
-            <v>Switch Fused Connection Unit - EF</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="B74" t="str">
-            <v>Switch Fused Connection Unit - Heat Interface Unit</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="B75" t="str">
-            <v>Switch Fused Connection Unit - IA</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="B76" t="str">
-            <v>Switch Fused Connection Unit - Washing Machine</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="B77" t="str">
-            <v>Switch Fused Connection Unit - Dish Washer</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="B78" t="str">
-            <v>Switch Fused Connection Unit - Fridge Freezer</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="B79" t="str">
-            <v>Switch Fused Connection Unit- HRV</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="B80" t="str">
-            <v>Switched Fused Connection Unit</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="B81" t="str">
-            <v>Switched Fused Connection Unit - ETR</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="B82" t="str">
-            <v>Telephone Outlet</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="B83" t="str">
-            <v>TP&amp;N Distribution Board</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="B84" t="str">
-            <v>TP&amp;N Isolator</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="B85" t="str">
-            <v>TP&amp;N Isolator - 20A</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="B86" t="str">
-            <v>TP&amp;N Isolator - 300A</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="B87" t="str">
-            <v>TP&amp;N Isolator - 32A</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="B88" t="str">
-            <v>TP&amp;N Isolator - 63A</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="B89" t="str">
-            <v>TV Socket</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="B90" t="str">
-            <v>Twin RJ45 Data Outlet</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="B91" t="str">
-            <v>Twin Switched Socket Outlet</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="B92" t="str">
-            <v>Unswitched Fused Connection Unit</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="B95" t="str">
-            <v>CONTAINMENT</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="B96" t="str">
-            <v>100mm x 25mm tray</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="B97" t="str">
-            <v>100mm x 50mm tray</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="B98" t="str">
-            <v>150mm x 150mm Trunking</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="B99" t="str">
-            <v>150mm x 25mm tray</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="B100" t="str">
-            <v>225mm x 25mm tray</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="B101" t="str">
-            <v>300mm x 25mm tray</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="B102" t="str">
-            <v>450mm x 25mm tray</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="B103" t="str">
-            <v>50mm x 25mm tray</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="B104" t="str">
-            <v>50mm x 25mm tray</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="B105" t="str">
-            <v>75mm x 25mm tray</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="B106" t="str">
-            <v>C Item 11</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="B107" t="str">
-            <v>C Item 12</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="B108" t="str">
-            <v>C Item 13</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="B109" t="str">
-            <v>C Item 14</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="B112" t="str">
-            <v>FIRE ALARM</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="B113" t="str">
-            <v>Fire Alarm Interface Unit</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="B114" t="str">
-            <v>Fire Alarm Sounder</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="B115" t="str">
-            <v>Smoke detectors</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="B116" t="str">
-            <v>Heat detectors</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="B117" t="str">
-            <v>CO2 detectors</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="B118" t="str">
-            <v>FA Item 4</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="B119" t="str">
-            <v>FA Item 5</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="B120" t="str">
-            <v>FA Item 6</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="B123" t="str">
-            <v>DISTRIBUTION</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="B124" t="str">
-            <v>D Item 1</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="B125" t="str">
-            <v>D Item 2</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="B126" t="str">
-            <v>D Item 3</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="B127" t="str">
-            <v>D Item 4</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="B128" t="str">
-            <v>D Item 5</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="B129" t="str">
-            <v>D Item 6</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="B130" t="str">
-            <v>D Item 7</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="B131" t="str">
-            <v>D Item 8</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="B134" t="str">
-            <v>MECHANICAL SUPPLIES</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="B135" t="str">
-            <v>MS Item 1</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="B136" t="str">
-            <v>MS Item 2</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="B137" t="str">
-            <v>MS Item 3</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="B138" t="str">
-            <v>MS Item 4</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="B139" t="str">
-            <v>MS Item 5</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="B140" t="str">
-            <v>MS Item 6</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="B141" t="str">
-            <v>MS Item 7</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="B142" t="str">
-            <v>MS Item 8</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="B145" t="str">
-            <v>VENTILATION</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="B146" t="str">
-            <v>V Item 1</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="B147" t="str">
-            <v>V Item 2</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="B148" t="str">
-            <v>V Item 3</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="B149" t="str">
-            <v>V Item 4</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="B150" t="str">
-            <v>V Item 5</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="B151" t="str">
-            <v>V Item 6</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="B152" t="str">
-            <v>V Item 7</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="B153" t="str">
-            <v>V Item 8</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="B156" t="str">
-            <v>ACCESS CONTROL &amp; SECURITY</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="B157" t="str">
-            <v>AC Item 1</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="B158" t="str">
-            <v>AC Item 2</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="B159" t="str">
-            <v>AC Item 3</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="B160" t="str">
-            <v>AC Item 4</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="B161" t="str">
-            <v>AC Item 5</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="B162" t="str">
-            <v>AC Item 6</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="B163" t="str">
-            <v>AC Item 7</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="B164" t="str">
-            <v>AC Item 8</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="B167" t="str">
-            <v>AUDIO VISUAL / TV / SATELITE</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="B168" t="str">
-            <v>AV ITEM 1</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="B169" t="str">
-            <v>AV ITEM 2</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="B170" t="str">
-            <v>AV ITEM 3</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="B171" t="str">
-            <v>AV ITEM 4</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="B172" t="str">
-            <v>AV ITEM 5</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="B173" t="str">
-            <v>AV ITEM 6</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="B174" t="str">
-            <v>AV ITEM 7</v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="B175" t="str">
-            <v>AV ITEM 8</v>
-          </cell>
-        </row>
-        <row r="178">
-          <cell r="B178" t="str">
-            <v>HEATING INTERFACE / CONTROLS</v>
-          </cell>
-        </row>
-        <row r="179">
-          <cell r="B179" t="str">
-            <v>HI Item 1</v>
-          </cell>
-        </row>
-        <row r="180">
-          <cell r="B180" t="str">
-            <v>HI Item 2</v>
-          </cell>
-        </row>
-        <row r="181">
-          <cell r="B181" t="str">
-            <v>HI Item 3</v>
-          </cell>
-        </row>
-        <row r="182">
-          <cell r="B182" t="str">
-            <v>HI Item 4</v>
-          </cell>
-        </row>
-        <row r="183">
-          <cell r="B183" t="str">
-            <v>HI Item 5</v>
-          </cell>
-        </row>
-        <row r="184">
-          <cell r="B184" t="str">
-            <v>HI Item 6</v>
-          </cell>
-        </row>
-        <row r="185">
-          <cell r="B185" t="str">
-            <v>HI Item 7</v>
-          </cell>
-        </row>
-        <row r="186">
-          <cell r="B186" t="str">
-            <v>HI Item 8</v>
-          </cell>
-        </row>
-        <row r="189">
-          <cell r="B189" t="str">
-            <v>MISCELLANEOUS</v>
-          </cell>
-        </row>
-        <row r="190">
-          <cell r="B190" t="str">
-            <v>Door Entry Handset</v>
-          </cell>
-        </row>
-        <row r="191">
-          <cell r="B191" t="str">
-            <v>Electric Meter</v>
-          </cell>
-        </row>
-        <row r="192">
-          <cell r="B192" t="str">
-            <v>Electric Towel Rail</v>
-          </cell>
-        </row>
-        <row r="193">
-          <cell r="B193" t="str">
-            <v>Flex Connection Outlet</v>
-          </cell>
-        </row>
-        <row r="194">
-          <cell r="B194" t="str">
-            <v>Ryefield Board</v>
-          </cell>
-        </row>
-        <row r="195">
-          <cell r="B195" t="str">
-            <v>SP&amp;N Distribution Board</v>
-          </cell>
-        </row>
-        <row r="196">
-          <cell r="B196" t="str">
-            <v>SP&amp;N Isolator</v>
-          </cell>
-        </row>
-        <row r="197">
-          <cell r="B197" t="str">
-            <v>Earthing &amp; bonding</v>
-          </cell>
-        </row>
-        <row r="198">
-          <cell r="B198" t="str">
-            <v>Surge protection</v>
-          </cell>
-        </row>
-        <row r="199">
-          <cell r="B199" t="str">
-            <v>M Item 3</v>
-          </cell>
-        </row>
-        <row r="200">
-          <cell r="B200" t="str">
-            <v>M Item 4</v>
-          </cell>
-        </row>
-        <row r="201">
-          <cell r="B201" t="str">
-            <v>M Item 5</v>
-          </cell>
-        </row>
-        <row r="202">
-          <cell r="B202" t="str">
-            <v>M Item 6</v>
-          </cell>
-        </row>
-        <row r="203">
-          <cell r="B203" t="str">
-            <v>M Item 7</v>
-          </cell>
-        </row>
-        <row r="204">
-          <cell r="B204" t="str">
-            <v>M Item 8</v>
-          </cell>
-        </row>
-        <row r="207">
-          <cell r="B207" t="str">
-            <v>PRELIMS</v>
-          </cell>
-        </row>
-        <row r="208">
-          <cell r="B208" t="str">
-            <v xml:space="preserve">O&amp;M's </v>
-          </cell>
-        </row>
-        <row r="209">
-          <cell r="B209" t="str">
-            <v xml:space="preserve">Testing and Commissioning </v>
-          </cell>
-        </row>
-        <row r="210">
-          <cell r="B210" t="str">
-            <v>Storage of tools and materials</v>
-          </cell>
-        </row>
-        <row r="211">
-          <cell r="B211" t="str">
-            <v>Project Management</v>
-          </cell>
-        </row>
-        <row r="212">
-          <cell r="B212" t="str">
-            <v>Access Towers</v>
-          </cell>
-        </row>
-        <row r="213">
-          <cell r="B213" t="str">
-            <v>P Item 2</v>
-          </cell>
-        </row>
-        <row r="214">
-          <cell r="B214" t="str">
-            <v>P Item 3</v>
-          </cell>
-        </row>
-        <row r="217">
-          <cell r="B217" t="str">
-            <v>SITE TEMPORARIES</v>
-          </cell>
-        </row>
-        <row r="218">
-          <cell r="B218" t="str">
-            <v>ST Item 1</v>
-          </cell>
-        </row>
-        <row r="219">
-          <cell r="B219" t="str">
-            <v>ST Item 2</v>
-          </cell>
-        </row>
-        <row r="220">
-          <cell r="B220" t="str">
-            <v>ST Item 3</v>
-          </cell>
-        </row>
-        <row r="221">
-          <cell r="B221" t="str">
-            <v>ST Item 4</v>
-          </cell>
-        </row>
-        <row r="222">
-          <cell r="B222" t="str">
-            <v>ST Item 5</v>
-          </cell>
-        </row>
-        <row r="223">
-          <cell r="B223" t="str">
-            <v>ST Item 6</v>
-          </cell>
-        </row>
-        <row r="224">
-          <cell r="B224" t="str">
-            <v>ST Item 7</v>
-          </cell>
-        </row>
-        <row r="225">
-          <cell r="B225" t="str">
-            <v>ST Item 8</v>
-          </cell>
-        </row>
-        <row r="228">
-          <cell r="B228" t="str">
-            <v>END</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Covering"/>
-      <sheetName val="Breakdown"/>
-      <sheetName val="Proc Sheet"/>
-      <sheetName val="Containment"/>
-      <sheetName val="Containment List"/>
-      <sheetName val="Lighting"/>
-      <sheetName val="Lighting List"/>
-      <sheetName val="Sockets"/>
-      <sheetName val="Sockets List"/>
-      <sheetName val="Switches"/>
-      <sheetName val="Switches List"/>
-      <sheetName val="Consumer_Unit"/>
-      <sheetName val="Consumer Unit List"/>
-      <sheetName val="Misc"/>
-      <sheetName val="Misc List"/>
-      <sheetName val="Other"/>
-      <sheetName val="Other List"/>
-      <sheetName val="Type List"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="10">
-          <cell r="E10">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Containment</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>Lighting</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>Sockets</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Switches</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Consumer Unit</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Misc</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>Other</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/outputs/Riverside House - Fenster Pricing Document (house format).xlsx
+++ b/outputs/Riverside House - Fenster Pricing Document (house format).xlsx
@@ -8,6 +8,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Document " sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Pricing Document '!$C$1:$I$45</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>

--- a/outputs/Riverside House - Fenster Pricing Document (house format).xlsx
+++ b/outputs/Riverside House - Fenster Pricing Document (house format).xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Document " sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Pricing Document '!$2:$7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Pricing Document '!$C$1:$I$45</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
